--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SvrProdFeeDealInterf.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SvrProdFeeDealInterf.xlsx
@@ -67,18 +67,21 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -112,14 +115,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,7 +435,7 @@
     <col min="2" max="2" width="17.375" customWidth="1"/>
     <col min="3" max="3" width="17.75" customWidth="1"/>
     <col min="4" max="4" width="27.75" customWidth="1"/>
-    <col min="5" max="5" width="24" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -445,10 +448,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SvrProdFeeDealInterf.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SvrProdFeeDealInterf.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
   </bookViews>
@@ -459,7 +454,7 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
-      <formula1>"托管费,管理费（固定）,管理费（超额）,销售费,申购费,赎回费,客户收益"</formula1>
+      <formula1>"托管费,管理费（固定）,管理费（超额）,销售费,申购费,赎回费"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
